--- a/basedatos_partidas/salida/descompuestos/CT-15-06-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-15-06-040.xlsx
@@ -591,10 +591,10 @@
         <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>113.78</v>
+        <v>107.78</v>
       </c>
     </row>
     <row r="16">
@@ -802,10 +802,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>124.76</v>
+        <v>118.76</v>
       </c>
       <c r="H24" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="25">
@@ -821,7 +821,7 @@
       </c>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="5" t="n">
-        <v>126.01</v>
+        <v>119.95</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-15-06-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-15-06-040.xlsx
@@ -539,10 +539,10 @@
         <v>1.02</v>
       </c>
       <c r="G10" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H10" t="n">
-        <v>59.16</v>
+        <v>69.36</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>9.5</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>30.4</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="12">
@@ -617,10 +617,10 @@
         <v>0.15</v>
       </c>
       <c r="G13" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="14">
@@ -643,10 +643,10 @@
         <v>0.28</v>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H14" t="n">
-        <v>3.92</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="15">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>107.78</v>
+        <v>152.85</v>
       </c>
     </row>
     <row r="16">
@@ -802,10 +802,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>118.76</v>
+        <v>163.83</v>
       </c>
       <c r="H24" t="n">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="25">
@@ -821,7 +821,7 @@
       </c>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="5" t="n">
-        <v>119.95</v>
+        <v>165.47</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-15-06-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-15-06-040.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 15 Herrería, carpintería y vidrios</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Vidrios y espejos</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
